--- a/database_proforma_invoice.xlsx
+++ b/database_proforma_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3E0595-D804-40DF-99AA-81FB22D19B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC05839E-ABBD-4ED8-835E-06C650E05D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Proforma Invoice No.</t>
   </si>
@@ -98,89 +98,6 @@
   </si>
   <si>
     <t>Prepared by Title</t>
-  </si>
-  <si>
-    <t>042/BSS-JOB/AB/VII/2026</t>
-  </si>
-  <si>
-    <t>S250551FLD-R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
-  </si>
-  <si>
-    <t>16 Desember 2025</t>
-  </si>
-  <si>
-    <t>24 Month</t>
-  </si>
-  <si>
-    <t>31 Jul 2026</t>
-  </si>
-  <si>
-    <t>1 Jul 2026</t>
-  </si>
-  <si>
-    <t>043/BSS-JOB/AB/VII/2026</t>
-  </si>
-  <si>
-    <t>7207250142</t>
-  </si>
-  <si>
-    <t>4500011424</t>
-  </si>
-  <si>
-    <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesinan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-  </si>
-  <si>
-    <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
-  </si>
-  <si>
-    <t>Maintenance Support Supervisor</t>
-  </si>
-  <si>
-    <t>PT Banggai Sentral Sulawesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
-</t>
-  </si>
-  <si>
-    <t>Ir. Ferry Tatimu</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>01 s/d 31 Juli 2026</t>
-  </si>
-  <si>
-    <t>7207250142-BSS-WCC-2026-019</t>
-  </si>
-  <si>
-    <t>7207250142-BSS-WO-2026-019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
-</t>
-  </si>
-  <si>
-    <t>7207250142-BSS-CTR-2026-019</t>
-  </si>
-  <si>
-    <t>Onesimus Suriadi</t>
-  </si>
-  <si>
-    <t>General Service Manager</t>
   </si>
 </sst>
 </file>
@@ -520,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.9296875" customWidth="1"/>
@@ -610,118 +527,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2">
-        <v>7207250142</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2">
-        <v>4500011424</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" t="s">
-        <v>47</v>
-      </c>
-      <c r="W3" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>51</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
